--- a/artfynd/A 47451-2022 artfynd.xlsx
+++ b/artfynd/A 47451-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47451-2022 artfynd.xlsx
+++ b/artfynd/A 47451-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97104753</v>
+        <v>92064703</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Resby 9:1, Sm</t>
+          <t>Aspelund, 290m NO, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563135.2642039545</v>
+        <v>563241</v>
       </c>
       <c r="R2" t="n">
-        <v>6268215.876847981</v>
+        <v>6268178</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,15 +762,20 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Kärrkant i frisk-våt talldominerad barrskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Eric Lundén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Eric Lundén, Frida Gustafsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -803,12 +785,7 @@
         <v>97104761</v>
       </c>
       <c r="B3" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563117.7261810796</v>
+        <v>563118</v>
       </c>
       <c r="R3" t="n">
-        <v>6268206.795664972</v>
+        <v>6268206</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,19 +854,9 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,41 +884,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97104759</v>
+        <v>97104751</v>
       </c>
       <c r="B4" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -961,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563117.7261810796</v>
+        <v>563196</v>
       </c>
       <c r="R4" t="n">
-        <v>6268206.795664972</v>
+        <v>6268156</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,19 +964,9 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,15 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97104758</v>
+        <v>97104753</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,7 +1024,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1086,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563117.7261810796</v>
+        <v>563136</v>
       </c>
       <c r="R5" t="n">
-        <v>6268206.795664972</v>
+        <v>6268216</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,19 +1074,9 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,6 +1101,218 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>97104758</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Resby 9:1, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>563118</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6268206</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>97104759</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Resby 9:1, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>563118</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6268206</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47451-2022 artfynd.xlsx
+++ b/artfynd/A 47451-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92064703</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97104761</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97104751</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97104753</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97104758</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,8 +1343,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97104759</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>